--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484210_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484210_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9088</v>
+        <v>5.8394</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9751</v>
+        <v>2.2208</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9338</v>
+        <v>3.6186</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2696</v>
+        <v>4.9439</v>
       </c>
       <c r="H2" t="n">
-        <v>3.054</v>
+        <v>2.2727</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2156</v>
+        <v>2.6711</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4894</v>
+        <v>3.9499</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5991</v>
+        <v>2.0875</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8902</v>
+        <v>1.8624</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2198</v>
+        <v>0.994</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4549</v>
+        <v>0.1852</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6747</v>
+        <v>0.8087</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4484</v>
+        <v>0.7002</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2716</v>
+        <v>0.2244</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1769</v>
+        <v>0.4758</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2022</v>
+        <v>4.7763</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0559</v>
+        <v>3.0332</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1463</v>
+        <v>1.7431</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5001</v>
+        <v>3.2696</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0591</v>
+        <v>3.054</v>
       </c>
       <c r="I3" t="n">
-        <v>2.441</v>
+        <v>0.2156</v>
       </c>
       <c r="J3" t="n">
-        <v>2.729</v>
+        <v>3.4894</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2318</v>
+        <v>2.5991</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4972</v>
+        <v>0.8902</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2289</v>
+        <v>-0.2198</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1727</v>
+        <v>0.4549</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9437</v>
+        <v>-0.6747</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5301</v>
+        <v>2.3159</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4171</v>
+        <v>1.3297</v>
       </c>
       <c r="U3" t="n">
-        <v>1.113</v>
+        <v>0.9862</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6093</v>
+        <v>0.1675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8865</v>
+        <v>0.1675</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8219</v>
+        <v>4.7346</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1346</v>
+        <v>2.9929</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6873</v>
+        <v>1.7417</v>
       </c>
       <c r="G4" t="n">
         <v>3.2387</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>0.892</v>
+        <v>0.8047</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8035</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0885</v>
+        <v>0.143</v>
       </c>
       <c r="V4" t="n">
         <v>0.8865</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7677</v>
+        <v>4.1585</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1492</v>
+        <v>3.5297</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6186</v>
+        <v>0.6288</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9439</v>
+        <v>2.5001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2727</v>
+        <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6711</v>
+        <v>2.441</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9499</v>
+        <v>2.729</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0875</v>
+        <v>1.2318</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8624</v>
+        <v>1.4972</v>
       </c>
       <c r="M5" t="n">
-        <v>0.994</v>
+        <v>-0.2289</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1852</v>
+        <v>-1.1727</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8087</v>
+        <v>0.9437</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3715</v>
+        <v>1.4864</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.8908</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4758</v>
+        <v>0.5955</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9929</v>
+        <v>3.7733</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4744</v>
+        <v>1.636</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5186</v>
+        <v>2.1373</v>
       </c>
       <c r="G6" t="n">
         <v>1.8699</v>
@@ -922,13 +922,13 @@
         <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9743</v>
+        <v>1.7546</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3936</v>
+        <v>0.5552</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5807</v>
+        <v>1.1994</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2186</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4122</v>
+        <v>2.9675</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0815</v>
+        <v>4.9309</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3308</v>
+        <v>-1.9634</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8663</v>
+        <v>4.2005</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2131</v>
+        <v>3.0264</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0793</v>
+        <v>1.1741</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4349</v>
+        <v>4.7547</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7598</v>
+        <v>2.9061</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6751</v>
+        <v>1.8486</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5686</v>
+        <v>-0.5542</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9729</v>
+        <v>0.1203</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4043</v>
+        <v>-0.6745</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4055</v>
+        <v>0.4815</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0689</v>
+        <v>0.1761</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3366</v>
+        <v>0.3053</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5545</v>
+        <v>-2.1052</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2786</v>
+        <v>2.8699</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4054</v>
+        <v>1.5664</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1268</v>
+        <v>1.3035</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2005</v>
+        <v>0.8663</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0264</v>
+        <v>-0.2131</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1741</v>
+        <v>1.0793</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7547</v>
+        <v>1.4349</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9061</v>
+        <v>0.7598</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8486</v>
+        <v>0.6751</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5542</v>
+        <v>-0.5686</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1203</v>
+        <v>-0.9729</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6745</v>
+        <v>0.4043</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5538</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3907</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2074</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.3494</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.1419</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-2.1052</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.1052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9283</v>
+        <v>2.1792</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4242</v>
+        <v>-1.4159</v>
       </c>
       <c r="F9" t="n">
-        <v>0.504</v>
+        <v>3.5951</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6897</v>
+        <v>0.373</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5209</v>
+        <v>0.2648</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2106</v>
+        <v>0.1082</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5976</v>
+        <v>-1.035</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9389</v>
+        <v>-1.1435</v>
       </c>
       <c r="L9" t="n">
-        <v>2.5365</v>
+        <v>0.1086</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9079</v>
+        <v>1.4079</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.582</v>
+        <v>1.4083</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6741</v>
+        <v>-0.0004</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7231</v>
+        <v>1.1384</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5614</v>
+        <v>0.3186</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1617</v>
+        <v>0.8198</v>
       </c>
       <c r="V9" t="n">
-        <v>1.8828</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3891</v>
+        <v>2.12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5752</v>
+        <v>1.2619</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9643</v>
+        <v>0.8581</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9379999999999999</v>
+        <v>0.6897</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5193</v>
+        <v>-2.5209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5813</v>
+        <v>3.2106</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6441</v>
+        <v>1.5976</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5513</v>
+        <v>-0.9389</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.09279999999999999</v>
+        <v>2.5365</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2939</v>
+        <v>-0.9079</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.968</v>
+        <v>-1.582</v>
       </c>
       <c r="O10" t="n">
         <v>0.6741</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3674</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2955</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0689</v>
+        <v>0.399</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2266</v>
+        <v>0.5158</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6642</v>
+        <v>1.8828</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
         <v>0.6642</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0513</v>
+        <v>1.5586</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3259</v>
+        <v>-0.5147</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3772</v>
+        <v>2.0732</v>
       </c>
       <c r="G11" t="n">
-        <v>0.373</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2648</v>
+        <v>-1.5193</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1082</v>
+        <v>0.5813</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.035</v>
+        <v>-0.6441</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1435</v>
+        <v>-0.5513</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1086</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4079</v>
+        <v>-0.2939</v>
       </c>
       <c r="N11" t="n">
-        <v>1.4083</v>
+        <v>-0.968</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0004</v>
+        <v>0.6741</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0104</v>
+        <v>0.465</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5915</v>
+        <v>0.1294</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6019</v>
+        <v>0.3356</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1143</v>
+        <v>1.1005</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1942</v>
+        <v>-0.4258</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3085</v>
+        <v>1.5264</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4082</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1123</v>
+        <v>1.0985</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1432</v>
+        <v>0.9115</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0309</v>
+        <v>0.187</v>
       </c>
       <c r="V12" t="n">
         <v>0.9962</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>34.8673</v>
+        <v>36.0778</v>
       </c>
       <c r="E13" t="n">
-        <v>17.605</v>
+        <v>18.8154</v>
       </c>
       <c r="F13" t="n">
-        <v>17.2626</v>
+        <v>17.2624</v>
       </c>
       <c r="G13" t="n">
         <v>20.6055</v>
       </c>
       <c r="H13" t="n">
-        <v>9.810799999999999</v>
+        <v>9.810799999999997</v>
       </c>
       <c r="I13" t="n">
         <v>10.7944</v>
@@ -1447,10 +1447,10 @@
         <v>11.3775</v>
       </c>
       <c r="L13" t="n">
-        <v>8.775099999999998</v>
+        <v>8.7751</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4528</v>
+        <v>0.4527999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-1.5668</v>
@@ -1468,13 +1468,13 @@
         <v>14.6507</v>
       </c>
       <c r="S13" t="n">
-        <v>10.8127</v>
+        <v>12.0232</v>
       </c>
       <c r="T13" t="n">
-        <v>4.94</v>
+        <v>6.150300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>5.872700000000001</v>
+        <v>5.872800000000002</v>
       </c>
       <c r="V13" t="n">
         <v>1.4958</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6909</v>
+        <v>4.0552</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5826</v>
+        <v>5.7849</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8917</v>
+        <v>-1.7297</v>
       </c>
       <c r="G14" t="n">
         <v>4.691</v>
@@ -1546,13 +1546,13 @@
         <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2187</v>
+        <v>-1.8544</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5131</v>
+        <v>-1.3108</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7056</v>
+        <v>-0.5436</v>
       </c>
       <c r="V14" t="n">
         <v>1.2186</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.492</v>
+        <v>1.8563</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4379</v>
+        <v>2.6401</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9459</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0.789</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8747</v>
+        <v>-1.5105</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2105</v>
+        <v>-1.0082</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6643</v>
+        <v>-0.5022</v>
       </c>
       <c r="V15" t="n">
         <v>2.3824</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1221</v>
+        <v>-0.1882</v>
       </c>
       <c r="E16" t="n">
-        <v>1.378</v>
+        <v>1.1758</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5001</v>
+        <v>-1.364</v>
       </c>
       <c r="G16" t="n">
         <v>0.4899</v>
@@ -1702,13 +1702,13 @@
         <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1981</v>
+        <v>-0.2641</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2175</v>
+        <v>0.0152</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4155</v>
+        <v>-0.2793</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6093</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7121</v>
+        <v>-2.297</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8472</v>
+        <v>-1.0494</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.865</v>
+        <v>-1.2476</v>
       </c>
       <c r="G17" t="n">
         <v>-4.1401</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6234</v>
+        <v>0.0385</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.22</v>
+        <v>-0.4222</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8434</v>
+        <v>0.4607</v>
       </c>
       <c r="V17" t="n">
         <v>1.2186</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7086</v>
+        <v>-2.8019</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8993</v>
+        <v>-3.1016</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1907</v>
+        <v>0.2997</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4724</v>
@@ -1858,13 +1858,13 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9041</v>
+        <v>-0.9974</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0083</v>
+        <v>-0.1939</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9124</v>
+        <v>-0.8035</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9414</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6488</v>
+        <v>-3.4738</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6512</v>
+        <v>-2.449</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9977</v>
+        <v>-1.0249</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1676</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2273</v>
+        <v>-0.0523</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2283</v>
+        <v>-0.0261</v>
       </c>
       <c r="U19" t="n">
-        <v>0.001</v>
+        <v>-0.0262</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4089</v>
+        <v>-4.5295</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0437</v>
+        <v>-0.1585</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.4527</v>
+        <v>-4.371</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3523</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7599</v>
+        <v>-0.8804</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0246</v>
+        <v>-0.2269</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7352</v>
+        <v>-0.6535</v>
       </c>
       <c r="V20" t="n">
         <v>-3.1014</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0383</v>
+        <v>-4.692</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8326</v>
+        <v>-3.7315</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2056</v>
+        <v>-0.9605</v>
       </c>
       <c r="G21" t="n">
         <v>-4.991</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7115</v>
+        <v>-0.3652</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4566</v>
+        <v>-0.3555</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2548</v>
+        <v>-0.0097</v>
       </c>
       <c r="V21" t="n">
         <v>0.6642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2329</v>
+        <v>-6.1059</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7812</v>
+        <v>-5.6801</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4518</v>
+        <v>-0.4259</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4233</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9463</v>
+        <v>-1.8193</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2105</v>
+        <v>-1.1093</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7359</v>
+        <v>-0.71</v>
       </c>
       <c r="V22" t="n">
         <v>0.3321</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1141</v>
+        <v>-7.4188</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2272</v>
+        <v>-5.5306</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8868</v>
+        <v>-1.8882</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8785</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6811</v>
+        <v>-1.9858</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8995</v>
+        <v>-1.2028</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7816</v>
+        <v>-0.7829</v>
       </c>
       <c r="V23" t="n">
         <v>0.0549</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.064399999999999</v>
+        <v>-8.5976</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.466</v>
+        <v>-5.1627</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5984</v>
+        <v>-3.435</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1499</v>
@@ -2326,13 +2326,13 @@
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9145</v>
+        <v>-0.4478</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3356</v>
+        <v>-0.0322</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5789</v>
+        <v>-0.4155</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4373</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-34.8673</v>
+        <v>-34.1932</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.2625</v>
+        <v>-17.2626</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.605</v>
+        <v>-16.9309</v>
       </c>
       <c r="G25" t="n">
         <v>-20.6052</v>
@@ -2404,13 +2404,13 @@
         <v>12.6973</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.8128</v>
+        <v>-10.1387</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.8729</v>
+        <v>-5.872699999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.9398</v>
+        <v>-4.2657</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4958</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484210_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484210_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8394</v>
+        <v>4.7763</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2208</v>
+        <v>3.0332</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6186</v>
+        <v>1.7431</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9439</v>
+        <v>3.2696</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2727</v>
+        <v>3.054</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6711</v>
+        <v>0.2156</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9499</v>
+        <v>3.4894</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0875</v>
+        <v>2.5991</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8624</v>
+        <v>0.8902</v>
       </c>
       <c r="M2" t="n">
-        <v>0.994</v>
+        <v>-0.2198</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1852</v>
+        <v>0.4549</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8087</v>
+        <v>-0.6747</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7002</v>
+        <v>2.3159</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2244</v>
+        <v>1.3297</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4758</v>
+        <v>0.9862</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.1675</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7763</v>
+        <v>4.4277</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0332</v>
+        <v>2.6859</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7431</v>
+        <v>1.7417</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2696</v>
+        <v>2.9317</v>
       </c>
       <c r="H3" t="n">
-        <v>3.054</v>
+        <v>2.2308</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2156</v>
+        <v>0.7009</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4894</v>
+        <v>3.091</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5991</v>
+        <v>2.9291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8902</v>
+        <v>0.1619</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2198</v>
+        <v>-0.1593</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4549</v>
+        <v>-0.6984</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6747</v>
+        <v>0.5391</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3159</v>
+        <v>0.8047</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3297</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9862</v>
+        <v>0.143</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1675</v>
+        <v>0.8865</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1675</v>
+        <v>0.8865</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7346</v>
+        <v>4.1585</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9929</v>
+        <v>3.5297</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7417</v>
+        <v>0.6288</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2387</v>
+        <v>2.5001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5378</v>
+        <v>0.0591</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7009</v>
+        <v>2.441</v>
       </c>
       <c r="J4" t="n">
-        <v>3.398</v>
+        <v>2.729</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2361</v>
+        <v>1.2318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1619</v>
+        <v>1.4972</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1593</v>
+        <v>-0.2289</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6984</v>
+        <v>-1.1727</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5391</v>
+        <v>0.9437</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8047</v>
+        <v>1.4864</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.8908</v>
       </c>
       <c r="U4" t="n">
-        <v>0.143</v>
+        <v>0.5955</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8865</v>
+        <v>-0.6093</v>
       </c>
       <c r="W4" t="n">
         <v>0.8865</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1585</v>
+        <v>3.7733</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5297</v>
+        <v>1.636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6288</v>
+        <v>2.1373</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5001</v>
+        <v>1.8699</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0591</v>
+        <v>0.5477</v>
       </c>
       <c r="I5" t="n">
-        <v>2.441</v>
+        <v>1.3221</v>
       </c>
       <c r="J5" t="n">
-        <v>2.729</v>
+        <v>1.0808</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2318</v>
+        <v>-0.2418</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4972</v>
+        <v>1.3225</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2289</v>
+        <v>0.7891</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1727</v>
+        <v>0.7895</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9437</v>
+        <v>-0.0004</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4864</v>
+        <v>1.7546</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8908</v>
+        <v>0.5552</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5955</v>
+        <v>1.1994</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +902,72 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7733</v>
+        <v>3.7045</v>
       </c>
       <c r="E6" t="n">
-        <v>1.636</v>
+        <v>0.0859</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1373</v>
+        <v>3.6186</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8699</v>
+        <v>2.8089</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5477</v>
+        <v>1.3518</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3221</v>
+        <v>1.4572</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0808</v>
+        <v>1.815</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2418</v>
+        <v>1.1665</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3225</v>
+        <v>0.6484</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7891</v>
+        <v>0.994</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7895</v>
+        <v>0.1852</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>0.8087</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7546</v>
+        <v>0.7002</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5552</v>
+        <v>0.2244</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1994</v>
+        <v>0.4758</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1052</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.12</v>
+        <v>2.1349</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2619</v>
+        <v>2.1349</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6897</v>
+        <v>2.1349</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5209</v>
+        <v>0.921</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2106</v>
+        <v>1.214</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5976</v>
+        <v>2.1349</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9389</v>
+        <v>0.921</v>
       </c>
       <c r="L10" t="n">
-        <v>2.5365</v>
+        <v>1.214</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9079</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.582</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9147999999999999</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.399</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5158</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8828</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5586</v>
+        <v>2.12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5147</v>
+        <v>1.2619</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0732</v>
+        <v>0.8581</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9379999999999999</v>
+        <v>0.6897</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5193</v>
+        <v>-2.5209</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5813</v>
+        <v>3.2106</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6441</v>
+        <v>1.5976</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5513</v>
+        <v>-0.9389</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.09279999999999999</v>
+        <v>2.5365</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2939</v>
+        <v>-0.9079</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.968</v>
+        <v>-1.582</v>
       </c>
       <c r="O11" t="n">
         <v>0.6741</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3674</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.465</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1294</v>
+        <v>0.399</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3356</v>
+        <v>0.5158</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6642</v>
+        <v>1.8828</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1005</v>
+        <v>1.5586</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4258</v>
+        <v>-0.5147</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5264</v>
+        <v>2.0732</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4082</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3016</v>
+        <v>-1.5193</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.7098</v>
+        <v>0.5813</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6025</v>
+        <v>-0.6441</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4326</v>
+        <v>-0.5513</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0351</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1944</v>
+        <v>-0.2939</v>
       </c>
       <c r="N12" t="n">
-        <v>0.869</v>
+        <v>-0.968</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6747</v>
+        <v>0.6741</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0985</v>
+        <v>0.465</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9115</v>
+        <v>0.1294</v>
       </c>
       <c r="U12" t="n">
-        <v>0.187</v>
+        <v>0.3356</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9962</v>
+        <v>0.6642</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2224</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,1004 +1483,1393 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>36.0778</v>
+        <v>1.1005</v>
       </c>
       <c r="E13" t="n">
-        <v>18.8154</v>
+        <v>-0.4258</v>
       </c>
       <c r="F13" t="n">
-        <v>17.2624</v>
+        <v>1.5264</v>
       </c>
       <c r="G13" t="n">
-        <v>20.6055</v>
+        <v>-0.4082</v>
       </c>
       <c r="H13" t="n">
-        <v>9.810799999999997</v>
+        <v>2.3016</v>
       </c>
       <c r="I13" t="n">
-        <v>10.7944</v>
+        <v>-2.7098</v>
       </c>
       <c r="J13" t="n">
-        <v>20.1527</v>
+        <v>-0.6025</v>
       </c>
       <c r="K13" t="n">
-        <v>11.3775</v>
+        <v>1.4326</v>
       </c>
       <c r="L13" t="n">
-        <v>8.7751</v>
+        <v>-2.0351</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4527999999999999</v>
+        <v>0.1944</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5668</v>
+        <v>0.869</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0193</v>
+        <v>-0.6747</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9535</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6971</v>
+        <v>-1.9534</v>
       </c>
       <c r="R13" t="n">
-        <v>14.6507</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>12.0232</v>
+        <v>1.0985</v>
       </c>
       <c r="T13" t="n">
-        <v>6.150300000000001</v>
+        <v>0.9115</v>
       </c>
       <c r="U13" t="n">
-        <v>5.872800000000002</v>
+        <v>0.187</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4958</v>
+        <v>0.9962</v>
       </c>
       <c r="W13" t="n">
-        <v>5.2094</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7137</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0552</v>
+        <v>0.307</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7849</v>
+        <v>0.307</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7297</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.691</v>
+        <v>0.307</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5475</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1435</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.5533</v>
+        <v>0.307</v>
       </c>
       <c r="K14" t="n">
-        <v>3.79</v>
+        <v>0.307</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7633</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8623</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2425</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6198</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8544</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3108</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5436</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8563</v>
+        <v>36.07789999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6401</v>
+        <v>18.8154</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7838000000000001</v>
+        <v>17.2624</v>
       </c>
       <c r="G15" t="n">
-        <v>0.789</v>
+        <v>20.6054</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2748</v>
+        <v>9.810899999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4858</v>
+        <v>10.7945</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9068</v>
+        <v>20.1527</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3126</v>
+        <v>11.3775</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5942</v>
+        <v>8.7751</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1178</v>
+        <v>0.4527999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0379</v>
+        <v>-1.5668</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0799</v>
+        <v>2.0193</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>1.9535</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-12.6971</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>14.6507</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5105</v>
+        <v>12.0232</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0082</v>
+        <v>6.150300000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5022</v>
+        <v>5.872800000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3824</v>
+        <v>1.4958</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7182</v>
+        <v>5.2094</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
-      </c>
+        <v>-3.7137</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1882</v>
+        <v>2.5272</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1758</v>
+        <v>4.2569</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.364</v>
+        <v>-1.7297</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4899</v>
+        <v>3.163</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9895</v>
+        <v>1.6265</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4996</v>
+        <v>1.5365</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3326</v>
+        <v>6.0253</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2922</v>
+        <v>2.869</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>3.1563</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8427</v>
+        <v>-2.8623</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3026</v>
+        <v>-1.2425</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5401</v>
+        <v>-1.6198</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2641</v>
+        <v>-1.8544</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0152</v>
+        <v>-1.3108</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2793</v>
+        <v>-0.5436</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.297</v>
+        <v>1.8563</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0494</v>
+        <v>2.6401</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2476</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.1401</v>
+        <v>0.789</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9836</v>
+        <v>1.2748</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.1565</v>
+        <v>-0.4858</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6738</v>
+        <v>2.9068</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0806</v>
+        <v>2.3126</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.5942</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4664</v>
+        <v>-2.1178</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.903</v>
+        <v>-1.0379</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5634</v>
+        <v>-1.0799</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0385</v>
+        <v>-1.5105</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4222</v>
+        <v>-1.0082</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4607</v>
+        <v>-0.5022</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>2.3824</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>1.7182</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8019</v>
+        <v>1.5279</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1016</v>
+        <v>1.5279</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2997</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4724</v>
+        <v>1.5279</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.187</v>
+        <v>0.921</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7146</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2668</v>
+        <v>1.5279</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6332</v>
+        <v>0.921</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7944</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5538</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3482</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9974</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1939</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8035</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4738</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.449</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0249</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1676</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3579</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8097</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4694</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4694</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6982</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8885</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8097</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0523</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0261</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0262</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5295</v>
+        <v>-0.1882</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1585</v>
+        <v>1.1758</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.371</v>
+        <v>-1.364</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3523</v>
+        <v>0.4899</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1878</v>
+        <v>0.9895</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5401</v>
+        <v>-0.4996</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9046</v>
+        <v>2.3326</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9046</v>
+        <v>2.2922</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2569</v>
+        <v>-1.8427</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7168</v>
+        <v>-1.3026</v>
       </c>
       <c r="O20" t="n">
         <v>-0.5401</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8804</v>
+        <v>-0.2641</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2269</v>
+        <v>0.0152</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6535</v>
+        <v>-0.2793</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.1014</v>
+        <v>-0.6093</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.692</v>
+        <v>-2.297</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7315</v>
+        <v>-1.0494</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9605</v>
+        <v>-1.2476</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.991</v>
+        <v>-4.1401</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3495</v>
+        <v>-0.9836</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6415</v>
+        <v>-3.1565</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.204</v>
+        <v>-0.6738</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1817</v>
+        <v>-0.0806</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0223</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.787</v>
+        <v>-3.4664</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1678</v>
+        <v>-0.903</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6192</v>
+        <v>-2.5634</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3652</v>
+        <v>0.0385</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3555</v>
+        <v>-0.4222</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0097</v>
+        <v>0.4607</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.1059</v>
+        <v>-2.8019</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6801</v>
+        <v>-3.1016</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4259</v>
+        <v>0.2997</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4233</v>
+        <v>-0.4724</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.2336</v>
+        <v>-1.187</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1897</v>
+        <v>0.7146</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.594</v>
+        <v>-1.2668</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.6749</v>
+        <v>-0.6332</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0809</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8293</v>
+        <v>0.7944</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5587</v>
+        <v>-0.5538</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2706</v>
+        <v>1.3482</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8193</v>
+        <v>-0.9974</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1093</v>
+        <v>-0.1939</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.71</v>
+        <v>-0.8035</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3321</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4188</v>
+        <v>-3.4738</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5306</v>
+        <v>-2.449</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8882</v>
+        <v>-1.0249</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.8785</v>
+        <v>-2.1676</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.0546</v>
+        <v>-1.3579</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8239</v>
+        <v>-0.8097</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.9603</v>
+        <v>-0.4694</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.0817</v>
+        <v>-0.4694</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9182</v>
+        <v>-1.6982</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9729</v>
+        <v>-0.8885</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9453</v>
+        <v>-0.8097</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9858</v>
+        <v>-0.0523</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2028</v>
+        <v>-0.0261</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7829</v>
+        <v>-0.0262</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.5976</v>
+        <v>-4.5295</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1627</v>
+        <v>-0.1585</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.435</v>
+        <v>-4.371</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1499</v>
+        <v>-0.3523</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6441</v>
+        <v>0.1878</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.5057</v>
+        <v>-0.5401</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9816</v>
+        <v>1.9046</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3888</v>
+        <v>1.9046</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3705</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1682</v>
+        <v>-2.2569</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.033</v>
+        <v>-1.7168</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1352</v>
+        <v>-0.5401</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4478</v>
+        <v>-0.8804</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0322</v>
+        <v>-0.2269</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4155</v>
+        <v>-0.6535</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.4373</v>
+        <v>-3.1014</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X24" t="n">
         <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-34.1932</v>
+        <v>-4.692</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.2626</v>
+        <v>-3.7315</v>
       </c>
       <c r="F25" t="n">
+        <v>-0.9605</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.991</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.3495</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-3.6415</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.204</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.1817</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.787</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.1678</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.6192</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.3652</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3555</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-6.4129</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.9871</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.4259</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.7303</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-4.5406</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.1897</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.901</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-3.9819</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.8293</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.5587</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.2706</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-1.8193</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1.1093</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F. VILAR FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-7.4188</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-5.5306</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.8882</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-5.8785</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-5.0546</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8239</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.9603</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-4.0817</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.9182</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.9729</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.9453</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-1.9858</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1.2028</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.7829</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>J. GALVE NAVARRO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-8.5976</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-5.1627</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-3.435</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-4.1499</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.6441</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-3.5057</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.9816</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-3.3705</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1.1682</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.033</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.1352</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.4478</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.4155</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484210_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-34.1933</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-17.2627</v>
+      </c>
+      <c r="F29" t="n">
         <v>-16.9309</v>
       </c>
-      <c r="G25" t="n">
-        <v>-20.6052</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-9.810699999999999</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="G29" t="n">
+        <v>-20.6053</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9.810700000000001</v>
+      </c>
+      <c r="I29" t="n">
         <v>-10.7944</v>
       </c>
-      <c r="J25" t="n">
-        <v>-0.4525999999999999</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.5667</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-2.019299999999999</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="J29" t="n">
+        <v>-0.4527000000000014</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.566700000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-2.0193</v>
+      </c>
+      <c r="M29" t="n">
         <v>-20.1526</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-11.3775</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>-8.7751</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-14.6508</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>-10.1387</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>-5.872699999999999</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>-4.2657</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>-1.4958</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>3.7136</v>
       </c>
-      <c r="X25" t="n">
-        <v>-5.209499999999999</v>
-      </c>
+      <c r="X29" t="n">
+        <v>-5.2095</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
